--- a/ExcelAnalyticsPlatform/ExcelAnalytics.API/Uploads/TestAllocation2.xlsx
+++ b/ExcelAnalyticsPlatform/ExcelAnalytics.API/Uploads/TestAllocation2.xlsx
@@ -134,9 +134,6 @@
     <t>Saira Malik T-2578</t>
   </si>
   <si>
-    <t>PK</t>
-  </si>
-  <si>
     <t>Lahore</t>
   </si>
   <si>
@@ -273,6 +270,9 @@
   </si>
   <si>
     <t>Rizwan Younas M-1567</t>
+  </si>
+  <si>
+    <t>CN</t>
   </si>
 </sst>
 </file>
@@ -848,10 +848,10 @@
         <v>35</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="S2" s="4">
         <v>6</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="3" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
@@ -898,10 +898,10 @@
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="K3" s="7">
         <v>46174</v>
@@ -921,11 +921,11 @@
       <c r="P3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S3" s="3">
         <v>5</v>
@@ -948,10 +948,10 @@
     </row>
     <row r="4" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>26</v>
@@ -969,13 +969,13 @@
         <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="K4" s="5">
         <v>45664</v>
@@ -990,16 +990,16 @@
         <v>75</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>35</v>
       </c>
       <c r="Q4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R4" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="S4" s="4">
         <v>4</v>
@@ -1022,16 +1022,16 @@
     </row>
     <row r="5" spans="1:24" ht="39" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>28</v>
@@ -1046,10 +1046,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="K5" s="7">
         <v>46204</v>
@@ -1064,16 +1064,16 @@
         <v>100</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S5" s="3">
         <v>7</v>
@@ -1096,16 +1096,16 @@
     </row>
     <row r="6" spans="1:24" ht="39" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>28</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K6" s="5">
         <v>46204</v>
@@ -1139,13 +1139,13 @@
         <v>34</v>
       </c>
       <c r="P6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R6" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="S6" s="4">
         <v>0</v>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="7" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>26</v>
@@ -1192,10 +1192,10 @@
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K7" s="7">
         <v>45938</v>
@@ -1216,10 +1216,10 @@
         <v>35</v>
       </c>
       <c r="Q7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R7" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S7" s="3">
         <v>6</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="8" spans="1:24" ht="39" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>26</v>
@@ -1269,7 +1269,7 @@
         <v>32</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K8" s="5">
         <v>45667</v>
@@ -1287,13 +1287,13 @@
         <v>34</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="S8" s="4">
         <v>2</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="9" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -1337,13 +1337,13 @@
         <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K9" s="7">
         <v>46062</v>
@@ -1364,10 +1364,10 @@
         <v>35</v>
       </c>
       <c r="Q9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S9" s="3">
         <v>5</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="10" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>26</v>
@@ -1414,10 +1414,10 @@
         <v>31</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K10" s="5">
         <v>46023</v>
@@ -1438,10 +1438,10 @@
         <v>35</v>
       </c>
       <c r="Q10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="S10" s="4">
         <v>5</v>
@@ -1464,16 +1464,16 @@
     </row>
     <row r="11" spans="1:24" ht="39" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="C11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K11" s="7">
         <v>46204</v>
@@ -1507,13 +1507,13 @@
         <v>34</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S11" s="3">
         <v>0</v>
@@ -1536,16 +1536,16 @@
     </row>
     <row r="12" spans="1:24" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>28</v>
@@ -1560,10 +1560,10 @@
         <v>31</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="K12" s="5">
         <v>45859</v>
@@ -1578,16 +1578,16 @@
         <v>100</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="Q12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="R12" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="S12" s="4">
         <v>6</v>
